--- a/stories/arbres/ATOM-SEC.RUE.002-09.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Constance va au marché. Elle marche avec maman. Maman est l'adulte. Elles arrivent au bord. Constance donne la main. La main est dans la main. Les pieds restent sur le trottoir. Elles restent sur le trottoir en attendant. Maman dit : on attend le feu vert. Constance sent la main de maman. Elle regarde maman. Le feu est vert. Maman dit : feu vert. On avance avec l'adulte. Constance tient la main. Elles marchent ensemble. Les fruits sentent le sucré. Constance dit : merci maman.</t>
+          <t>Constance va au marché. Elle marche avec maman. Maman est l'adulte. Elles arrivent au bord. Constance donne la main. La main est dans la main. Les pieds restent sur le trottoir. Elles restent sur le trottoir en attendant. On attend le feu vert. Constance sent la main de maman. Elle regarde maman. Le feu est vert. Feu vert. On avance avec l'adulte. Constance tient la main. Elles marchent ensemble. Les fruits sentent le sucré. Merci maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Constance va au marché. Elle marche avec maman. Maman est l'adulte. Elles arrivent au bord. Constance donne la main. La main est dans la main. Les pieds restent sur le trottoir. Elles restent sur le trottoir en attendant.
+maman|On attend le feu vert.
+narrateur|Constance sent la main de maman. Elle regarde maman. Le feu est vert.
+maman|Feu vert. On avance avec l'adulte.
+narrateur|Constance tient la main. Elles marchent ensemble. Les fruits sentent le sucré.
+enfant-f|Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Constance est avec maman. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1672,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Constance a donné la main. Elle a attendu le feu vert. Maman, l'adulte, était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1843,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Constance serre la main de maman. Elles tiennent un sac de pommes.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2010,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2050,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-09.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 enfant-f|Merci maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Constance est avec maman. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1677,6 +1684,7 @@
           <t>narrateur|Constance a donné la main. Elle a attendu le feu vert. Maman, l'adulte, était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1848,6 +1856,7 @@
           <t>narrateur|Constance serre la main de maman. Elles tiennent un sac de pommes.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2015,6 +2024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2067,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2258,6 +2282,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.002-09.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Constance attend le feu vert au marché</t>
+          <t>La cagette rouge</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorina veut une fraise dans la cagette rouge. Une pêche roule. Au bord, elle attend le feu vert, la main dans la main. Puis le jus sucré.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Constance va au marché. Elle marche avec maman. Maman est l'adulte. Elles arrivent au bord. Constance donne la main. La main est dans la main. Les pieds restent sur le trottoir. Elles restent sur le trottoir en attendant. On attend le feu vert. Constance sent la main de maman. Elle regarde maman. Le feu est vert. Feu vert. On avance avec l'adulte. Constance tient la main. Elles marchent ensemble. Les fruits sentent le sucré. Merci maman.</t>
+          <t>Le bois des cagettes craque sous le soleil. Les fraises brillent, toutes rouges. Ça sent le sucré et le bois chaud. Une pêche ronde dort tout au bord. Le marché chante un peu plus loin. Victorina vit ici, avec maman. Maman, les fraises brillent ! Oui. Elles sentent le soleil. Tu as vu la cagette rouge ? Elle est trop belle. En ce moment, Victorina tend la main. La main de maman est douce. Elles marchent sur le trottoir. Le bois des cagettes craque encore. Je veux une fraise ! Bientôt. On reste sur le trottoir. Une pêche roule tout doux. Elle s'arrête près d'une caisse. La pêche ! On la verra après. Le bord du trottoir arrive. Une petite lumière rouge attend. On s'arrête. On attend le feu vert. Tu donnes la main ? Victorina serre la main. Ses pieds restent sur le trottoir. J'attends. Bravo. Une abeille tourne au-dessus des fruits. Les fraises sentent plus fort. Elle bourdonne ! Oui. On attend encore ? Oui, maman. La lumière reste rouge un peu. Victorina sent le sucré tout près. Tu tiens bien ma main ? Oui. Puis la lumière devient verte. Feu vert. On avance avec maman. Elles avancent ensemble, tout doux. Victorina garde la main. La cagette rouge est tout près. Ça sent trop bon ! Merci d'avoir attendu. Le bois chaud craque encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Constance va au marché. Elle marche avec maman. Maman est l'adulte. Elles arrivent au bord. Constance donne la main. La main est dans la main. Les pieds restent sur le trottoir. Elles restent sur le trottoir en attendant. Maman dit : on attend le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Constance sent la main de maman. Elle regarde maman. Le feu est vert. Maman dit : feu vert. On avance avec l'adulte. Constance tient la main. Elles marchent ensemble. Les fruits sentent le sucré. Constance dit : merci maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bois des cagettes craque sous le soleil. Les fraises brillent, toutes rouges. Ça sent le sucré et le bois chaud. Une pêche ronde dort tout au bord. Le marché chante un peu plus loin. Victorina vit ici, avec maman. Maman, les fraises brillent ! Oui. Elles sentent le soleil. Tu as vu la cagette rouge ? Elle est trop belle. En ce moment, Victorina tend la main. La main de maman est douce. Elles marchent sur le trottoir. Le bois des cagettes craque encore. Je veux une fraise ! Bientôt. On reste sur le trottoir. Une pêche roule tout doux. Elle s'arrête près d'une caisse. La pêche ! On la verra après. Le bord du trottoir arrive. Une petite lumière rouge attend. On s'arrête. On attend le feu vert. Tu donnes la main ? Victorina serre la main. Ses pieds restent sur le trottoir. J'attends. Bravo. Une abeille tourne au-dessus des fruits. Les fraises sentent plus fort. Elle bourdonne ! Oui. On attend encore ? Oui, maman. La lumière reste rouge un peu. Victorina sent le sucré tout près. Tu tiens bien ma main ? Oui. Puis la lumière devient verte. Feu vert. On avance avec maman. Elles avancent ensemble, tout doux. Victorina garde la main. La cagette rouge est tout près. Ça sent trop bon ! Merci d'avoir attendu. Le bois chaud craque encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Constance va au marché. Elle marche avec maman. Maman est l'adulte. Elles arrivent au bord. Constance donne la main. La main est dans la main. Les pieds restent sur le trottoir. Elles restent sur le trottoir en attendant.
+          <t>narrateur|Le bois des cagettes craque sous le soleil.
+narrateur|Les fraises brillent, toutes rouges.
+narrateur|Ça sent le sucré et le bois chaud.
+narrateur|Une pêche ronde dort tout au bord.
+narrateur|Le marché chante un peu plus loin.
+narrateur|Victorina vit ici, avec maman.
+enfant-f|Maman, les fraises brillent !
+maman|Oui.
+maman|Elles sentent le soleil.
+maman|Tu as vu la cagette rouge ?
+enfant-f|Elle est trop belle.
+narrateur|En ce moment, Victorina tend la main.
+narrateur|La main de maman est douce.
+narrateur|Elles marchent sur le trottoir.
+narrateur|Le bois des cagettes craque encore.
+enfant-f|Je veux une fraise !
+maman|Bientôt.
+maman|On reste sur le trottoir.
+narrateur|Une pêche roule tout doux.
+narrateur|Elle s'arrête près d'une caisse.
+enfant-f|La pêche !
+maman|On la verra après.
+narrateur|Le bord du trottoir arrive.
+narrateur|Une petite lumière rouge attend.
+maman|On s'arrête.
 maman|On attend le feu vert.
-narrateur|Constance sent la main de maman. Elle regarde maman. Le feu est vert.
-maman|Feu vert. On avance avec l'adulte.
-narrateur|Constance tient la main. Elles marchent ensemble. Les fruits sentent le sucré.
-enfant-f|Merci maman.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Tu donnes la main ?
+narrateur|Victorina serre la main.
+narrateur|Ses pieds restent sur le trottoir.
+enfant-f|J'attends.
+maman|Bravo.
+narrateur|Une abeille tourne au-dessus des fruits.
+narrateur|Les fraises sentent plus fort.
+enfant-f|Elle bourdonne !
+maman|Oui.
+maman|On attend encore ?
+enfant-f|Oui, maman.
+narrateur|La lumière reste rouge un peu.
+narrateur|Victorina sent le sucré tout près.
+maman|Tu tiens bien ma main ?
+enfant-f|Oui.
+narrateur|Puis la lumière devient verte.
+maman|Feu vert.
+maman|On avance avec maman.
+narrateur|Elles avancent ensemble, tout doux.
+narrateur|Victorina garde la main.
+narrateur|La cagette rouge est tout près.
+enfant-f|Ça sent trop bon !
+maman|Merci d'avoir attendu.
+narrateur|Le bois chaud craque encore.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>marche</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1405,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Constance est avec maman. Que fait-elle ?</t>
+          <t>Victorina est avec maman. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Constance est avec maman. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina est avec maman. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1360,12 +1420,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>feu vert</t>
+          <t>attendre le feu vert</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>feu vert | la main | avec maman | avec l'adulte | attendre</t>
+          <t>attendre | feu vert | la main | avec maman | elle attend | donner la main</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1440,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle donne la main. Elle attend le feu vert. Que fait Constance ?</t>
+          <t>Elle attend le feu vert. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1489,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1565,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Constance est avec maman. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorina est avec maman.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Constance a donné la main. Elle a attendu le feu vert. Maman, l'adulte, était là.</t>
+          <t>Victorina a donné la main. Elle a attendu le feu vert. Ses pieds sont restés au bord. Tu as attendu le feu vert ? Oui. J'ai donné la main. Bravo, Victorina. On avance avec maman. La main de maman reste douce. Les fraises brillent plus fort. La pêche dort encore près de la caisse.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Constance a donné la main. Elle a attendu le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Maman, l'adulte, était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a donné la main. Elle a attendu le feu vert. Ses pieds sont restés au bord. Tu as attendu le feu vert ? Oui. J'ai donné la main. Bravo, Victorina. On avance avec maman. La main de maman reste douce. Les fraises brillent plus fort. La pêche dort encore près de la caisse.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,14 +1654,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1681,10 +1741,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Constance a donné la main. Elle a attendu le feu vert. Maman, l'adulte, était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorina a donné la main.
+narrateur|Elle a attendu le feu vert.
+narrateur|Ses pieds sont restés au bord.
+maman|Tu as attendu le feu vert ?
+enfant-f|Oui.
+enfant-f|J'ai donné la main.
+maman|Bravo, Victorina.
+maman|On avance avec maman.
+narrateur|La main de maman reste douce.
+narrateur|Les fraises brillent plus fort.
+narrateur|La pêche dort encore près de la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1709,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Constance serre la main de maman. Elles tiennent un sac de pommes.</t>
+          <t>Maman parle à l'étal. Tu prends une fraise ? Victorina tient une fraise tiède. Elle est sucrée ! Oui. Tu as bien attendu. Le jus brille un peu au coin des lèvres. Le bois de la cagette est rêche. Et la pêche ? Elle reste à l'étal. Elles tiennent encore la main. Le marché sent le sucré et le thym. Une cagette vide sonne tout creux. Elle fait toc ! Oui. Et toi, tu as gardé la main. Victorina lèche un doigt rouge. Le soleil chauffe encore le bois.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Constance serre la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Elles tiennent un sac de pommes.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman parle à l'étal. Tu prends une fraise ? Victorina tient une fraise tiède. Elle est sucrée ! Oui. Tu as bien attendu. Le jus brille un peu au coin des lèvres. Le bois de la cagette est rêche. Et la pêche ? Elle reste à l'étal. Elles tiennent encore la main. Le marché sent le sucré et le thym. Une cagette vide sonne tout creux. Elle fait toc ! Oui. Et toi, tu as gardé la main. Victorina lèche un doigt rouge. Le soleil chauffe encore le bois.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,14 +1839,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1853,10 +1922,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Constance serre la main de maman. Elles tiennent un sac de pommes.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman parle à l'étal.
+maman|Tu prends une fraise ?
+narrateur|Victorina tient une fraise tiède.
+enfant-f|Elle est sucrée !
+maman|Oui.
+maman|Tu as bien attendu.
+narrateur|Le jus brille un peu au coin des lèvres.
+narrateur|Le bois de la cagette est rêche.
+enfant-f|Et la pêche ?
+maman|Elle reste à l'étal.
+narrateur|Elles tiennent encore la main.
+narrateur|Le marché sent le sucré et le thym.
+narrateur|Une cagette vide sonne tout creux.
+enfant-f|Elle fait toc !
+maman|Oui.
+maman|Et toi, tu as gardé la main.
+narrateur|Victorina lèche un doigt rouge.
+narrateur|Le soleil chauffe encore le bois.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1881,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La fraise sent le soleil. Oui. Merci d'être restée près. Une abeille s'éloigne. La cagette rouge reste pleine. Le jus de fraise brille sur ses doigts.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La fraise sent le soleil. Oui. Merci d'être restée près. Une abeille s'éloigne. La cagette rouge reste pleine. Le jus de fraise brille sur ses doigts.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1942,14 +2027,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2021,10 +2106,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|La fraise sent le soleil.
+maman|Oui.
+maman|Merci d'être restée près.
+narrateur|Une abeille s'éloigne.
+narrateur|La cagette rouge reste pleine.
+narrateur|Le jus de fraise brille sur ses doigts.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2043,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2081,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-09.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-09.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers le marché</t>
+          <t>trottoir vers le marché, cagettes au soleil</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Constance, maman</t>
+          <t>Victorina, maman</t>
         </is>
       </c>
     </row>
